--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EE07BE-C766-451F-993B-F9F9EDE16768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,106 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+  <si>
+    <t>MCU引脚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外设实例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有效电平</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>板上连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOC Pin13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXTI0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>User KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLUE LED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>按下低电平</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>低电平点亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +131,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +168,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +470,101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="20.149999999999999" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="13.78515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.0703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16" style="2" customWidth="1"/>
+    <col min="8" max="8" width="26.2109375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63EE07BE-C766-451F-993B-F9F9EDE16768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB140911-85A2-4CB4-A32D-9DA4BC9DC55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
   <si>
     <t>MCU引脚</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,6 +116,70 @@
   </si>
   <si>
     <t>低电平点亮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART1_TX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART1_RX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UART1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PB6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PB7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C_SCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C_SDA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOB Pin6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOB Pin7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DHT20、MPU6050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件I2C</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -471,16 +535,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="20.149999999999999" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="13.78515625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23" style="2" customWidth="1"/>
+    <col min="4" max="5" width="16.0703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.0703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16" style="2" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" style="2" customWidth="1"/>
     <col min="8" max="8" width="26.2109375" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -563,6 +626,98 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
+++ b/RTT_elog_DMA_UART_ring_project/00_Doc/01_资源分配表/02_MCU_PIN_MAP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\my_project_2026\Git_test\stm32f4_DMA_UART_ring_RTOS\RTT_elog_DMA_UART_ring_project\00_Doc\01_资源分配表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB140911-85A2-4CB4-A32D-9DA4BC9DC55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5474E8BC-216C-4CFC-ADE7-AF55309F21EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>MCU引脚</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +180,86 @@
   </si>
   <si>
     <t>软件I2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PB10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_CLK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_DC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_MOSI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_RST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD_BACK_LIGHT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOA Pin1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIOB Pin10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SPI1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -535,11 +615,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="20.149999999999999" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="13.78515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="2" customWidth="1"/>
     <col min="3" max="3" width="23" style="2" customWidth="1"/>
     <col min="4" max="5" width="16.0703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.0703125" style="2" customWidth="1"/>
@@ -718,6 +798,96 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
